--- a/Kachi_Gun/Table/Zombie.xlsx
+++ b/Kachi_Gun/Table/Zombie.xlsx
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>366</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>2.23k</t>
+          <t>1.11k</t>
         </is>
       </c>
     </row>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>139</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>6.82k</t>
+          <t>3.41k</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>426</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>20.8k</t>
+          <t>10.4k</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>2.6k</t>
+          <t>1.3k</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>63.5k</t>
+          <t>31.7k</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>7.94k</t>
+          <t>3.97k</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>193k</t>
+          <t>96.9k</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>24.2k</t>
+          <t>12.1k</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>591k</t>
+          <t>295k</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>73.9k</t>
+          <t>36.9k</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>1.8m</t>
+          <t>902k</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>204k</t>
+          <t>102k</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>3.74m</t>
+          <t>1.87m</t>
         </is>
       </c>
     </row>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>385k</t>
+          <t>192k</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>7.04m</t>
+          <t>3.52m</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>727k</t>
+          <t>363k</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>13.2m</t>
+          <t>6.63m</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>1.36m</t>
+          <t>684k</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>24.9m</t>
+          <t>12.4m</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>2.57m</t>
+          <t>1.28m</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>47m</t>
+          <t>23.5m</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>4.85m</t>
+          <t>2.42m</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>88.6m</t>
+          <t>44.3m</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>9.15m</t>
+          <t>4.57m</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>167m</t>
+          <t>83.5m</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>17.2m</t>
+          <t>8.61m</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>314m</t>
+          <t>157m</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>32.4m</t>
+          <t>16.2m</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>592m</t>
+          <t>296m</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>61.1m</t>
+          <t>30.5m</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>1.11b</t>
+          <t>558m</t>
         </is>
       </c>
     </row>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>115m</t>
+          <t>57.5m</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>2.1b</t>
+          <t>1.05b</t>
         </is>
       </c>
     </row>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>216m</t>
+          <t>108m</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>3.96b</t>
+          <t>1.98b</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>408m</t>
+          <t>204m</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>7.45b</t>
+          <t>3.72b</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>769m</t>
+          <t>384m</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>14b</t>
+          <t>7.02b</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>1.44b</t>
+          <t>724m</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>26.4b</t>
+          <t>13.2b</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>2.73b</t>
+          <t>1.36b</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>49.8b</t>
+          <t>24.9b</t>
         </is>
       </c>
     </row>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>5.14b</t>
+          <t>2.57b</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>93.8b</t>
+          <t>46.9b</t>
         </is>
       </c>
     </row>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>9.28b</t>
+          <t>4.64b</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>156b</t>
+          <t>78b</t>
         </is>
       </c>
     </row>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>14.1b</t>
+          <t>7.07b</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>238b</t>
+          <t>119b</t>
         </is>
       </c>
     </row>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>21.5b</t>
+          <t>10.7b</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>362b</t>
+          <t>181b</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>32.9b</t>
+          <t>16.4b</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>553b</t>
+          <t>276b</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>50.1b</t>
+          <t>25b</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>843b</t>
+          <t>421b</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>76.4b</t>
+          <t>38.2b</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>1.28t</t>
+          <t>643b</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>116b</t>
+          <t>58.3b</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>1.96t</t>
+          <t>980b</t>
         </is>
       </c>
     </row>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>177b</t>
+          <t>88.8b</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>2.98t</t>
+          <t>1.49t</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>271b</t>
+          <t>135b</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>4.55t</t>
+          <t>2.27t</t>
         </is>
       </c>
     </row>
@@ -3586,7 +3586,7 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>413b</t>
+          <t>206b</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>6.94t</t>
+          <t>3.47t</t>
         </is>
       </c>
     </row>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>629b</t>
+          <t>314b</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>10.5t</t>
+          <t>5.29t</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>960b</t>
+          <t>480b</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>16.1t</t>
+          <t>8.07t</t>
         </is>
       </c>
     </row>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>1.46t</t>
+          <t>732b</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>24.6t</t>
+          <t>12.3t</t>
         </is>
       </c>
     </row>
@@ -3826,7 +3826,7 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>2.23t</t>
+          <t>1.11t</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>37.5t</t>
+          <t>18.7t</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>3.4t</t>
+          <t>1.7t</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>57.2t</t>
+          <t>28.6t</t>
         </is>
       </c>
     </row>
@@ -3946,7 +3946,7 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>5.18t</t>
+          <t>2.59t</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>87.2t</t>
+          <t>43.6t</t>
         </is>
       </c>
     </row>
@@ -4006,7 +4006,7 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>7.91t</t>
+          <t>3.95t</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>133t</t>
+          <t>66.5t</t>
         </is>
       </c>
     </row>
@@ -4066,7 +4066,7 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>12t</t>
+          <t>6.02t</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>202t</t>
+          <t>101t</t>
         </is>
       </c>
     </row>
@@ -4126,7 +4126,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>18.3t</t>
+          <t>9.19t</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>309t</t>
+          <t>154t</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>28t</t>
+          <t>14t</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>471t</t>
+          <t>235t</t>
         </is>
       </c>
     </row>
@@ -4246,7 +4246,7 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>42.7t</t>
+          <t>21.3t</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>718t</t>
+          <t>359t</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>65.1t</t>
+          <t>32.5t</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>1.09aa</t>
+          <t>547t</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>99.3t</t>
+          <t>49.6t</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>1.67aa</t>
+          <t>835t</t>
         </is>
       </c>
     </row>
@@ -4426,7 +4426,7 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>151t</t>
+          <t>75.7t</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>2.54aa</t>
+          <t>1.27aa</t>
         </is>
       </c>
     </row>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>230t</t>
+          <t>115t</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>3.88aa</t>
+          <t>1.94aa</t>
         </is>
       </c>
     </row>
@@ -4546,7 +4546,7 @@
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>342t</t>
+          <t>171t</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>6.03aa</t>
+          <t>3.01aa</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>456t</t>
+          <t>228t</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>8.03aa</t>
+          <t>4.01aa</t>
         </is>
       </c>
     </row>
@@ -4666,7 +4666,7 @@
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>607t</t>
+          <t>303t</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>10.7aa</t>
+          <t>5.35aa</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>809t</t>
+          <t>404t</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>14.2aa</t>
+          <t>7.12aa</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>1.07aa</t>
+          <t>539t</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>18.9aa</t>
+          <t>9.49aa</t>
         </is>
       </c>
     </row>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>1.43aa</t>
+          <t>718t</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>25.2aa</t>
+          <t>12.6aa</t>
         </is>
       </c>
     </row>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>1.91aa</t>
+          <t>956t</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>33.6aa</t>
+          <t>16.8aa</t>
         </is>
       </c>
     </row>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>2.54aa</t>
+          <t>1.27aa</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>44.8aa</t>
+          <t>22.4aa</t>
         </is>
       </c>
     </row>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>3.39aa</t>
+          <t>1.69aa</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>59.7aa</t>
+          <t>29.8aa</t>
         </is>
       </c>
     </row>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>4.51aa</t>
+          <t>2.25aa</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>79.5aa</t>
+          <t>39.7aa</t>
         </is>
       </c>
     </row>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>6.01aa</t>
+          <t>3aa</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>105aa</t>
+          <t>52.9aa</t>
         </is>
       </c>
     </row>
@@ -5206,7 +5206,7 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>8.01aa</t>
+          <t>4aa</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>141aa</t>
+          <t>70.5aa</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>10.6aa</t>
+          <t>5.33aa</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>188aa</t>
+          <t>94aa</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>14.2aa</t>
+          <t>7.11aa</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t>250aa</t>
+          <t>125aa</t>
         </is>
       </c>
     </row>
@@ -5386,7 +5386,7 @@
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>18.9aa</t>
+          <t>9.47aa</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>333aa</t>
+          <t>166aa</t>
         </is>
       </c>
     </row>
@@ -5446,7 +5446,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>25.2aa</t>
+          <t>12.6aa</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t>444aa</t>
+          <t>222aa</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>33.6aa</t>
+          <t>16.8aa</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>591aa</t>
+          <t>295aa</t>
         </is>
       </c>
     </row>
@@ -5566,7 +5566,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>44.7aa</t>
+          <t>22.3aa</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
-          <t>788aa</t>
+          <t>394aa</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>59.6aa</t>
+          <t>29.8aa</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>1.04ab</t>
+          <t>524aa</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>79.4aa</t>
+          <t>39.7aa</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
@@ -5726,7 +5726,7 @@
       </c>
       <c r="L71" s="3" t="inlineStr">
         <is>
-          <t>1.39ab</t>
+          <t>699aa</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>105aa</t>
+          <t>52.8aa</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>1.86ab</t>
+          <t>931aa</t>
         </is>
       </c>
     </row>
@@ -5806,7 +5806,7 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>140aa</t>
+          <t>70.4aa</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="L73" s="3" t="inlineStr">
         <is>
-          <t>2.48ab</t>
+          <t>1.24ab</t>
         </is>
       </c>
     </row>
@@ -5866,7 +5866,7 @@
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>187aa</t>
+          <t>93.8aa</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>3.3ab</t>
+          <t>1.65ab</t>
         </is>
       </c>
     </row>
@@ -5926,7 +5926,7 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>249aa</t>
+          <t>124aa</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="L75" s="3" t="inlineStr">
         <is>
-          <t>4.4ab</t>
+          <t>2.2ab</t>
         </is>
       </c>
     </row>
@@ -5986,7 +5986,7 @@
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>332aa</t>
+          <t>166aa</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>5.86ab</t>
+          <t>2.93ab</t>
         </is>
       </c>
     </row>
@@ -6046,7 +6046,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>443aa</t>
+          <t>221aa</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="L77" s="3" t="inlineStr">
         <is>
-          <t>7.8ab</t>
+          <t>3.9ab</t>
         </is>
       </c>
     </row>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>590aa</t>
+          <t>295aa</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>10.3ab</t>
+          <t>5.19ab</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>786aa</t>
+          <t>393aa</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="L79" s="3" t="inlineStr">
         <is>
-          <t>13.8ab</t>
+          <t>6.92ab</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>1.04ab</t>
+          <t>523aa</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>18.4ab</t>
+          <t>9.22ab</t>
         </is>
       </c>
     </row>
@@ -6286,7 +6286,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>1.39ab</t>
+          <t>697aa</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="L81" s="3" t="inlineStr">
         <is>
-          <t>24.5ab</t>
+          <t>12.2ab</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>1.85ab</t>
+          <t>929aa</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>32.7ab</t>
+          <t>16.3ab</t>
         </is>
       </c>
     </row>
@@ -6406,7 +6406,7 @@
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>2.47ab</t>
+          <t>1.23ab</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="L83" s="3" t="inlineStr">
         <is>
-          <t>43.5ab</t>
+          <t>21.7ab</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>3.29ab</t>
+          <t>1.64ab</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="L84" s="3" t="inlineStr">
         <is>
-          <t>58ab</t>
+          <t>29ab</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>4.39ab</t>
+          <t>2.19ab</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="L85" s="3" t="inlineStr">
         <is>
-          <t>77.3ab</t>
+          <t>38.6ab</t>
         </is>
       </c>
     </row>
@@ -6586,7 +6586,7 @@
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>5.84ab</t>
+          <t>2.92ab</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="L86" s="3" t="inlineStr">
         <is>
-          <t>102ab</t>
+          <t>51.4ab</t>
         </is>
       </c>
     </row>
@@ -6646,7 +6646,7 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>7.79ab</t>
+          <t>3.89ab</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="L87" s="3" t="inlineStr">
         <is>
-          <t>137ab</t>
+          <t>68.5ab</t>
         </is>
       </c>
     </row>
@@ -6706,7 +6706,7 @@
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>10.3ab</t>
+          <t>5.18ab</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="L88" s="3" t="inlineStr">
         <is>
-          <t>182ab</t>
+          <t>91.3ab</t>
         </is>
       </c>
     </row>
@@ -6766,7 +6766,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>13.8ab</t>
+          <t>6.91ab</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="L89" s="3" t="inlineStr">
         <is>
-          <t>243ab</t>
+          <t>121ab</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>18.4ab</t>
+          <t>9.2ab</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="L90" s="3" t="inlineStr">
         <is>
-          <t>324ab</t>
+          <t>162ab</t>
         </is>
       </c>
     </row>
@@ -6886,7 +6886,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>24.5ab</t>
+          <t>12.2ab</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="L91" s="3" t="inlineStr">
         <is>
-          <t>431ab</t>
+          <t>215ab</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>32.6ab</t>
+          <t>16.3ab</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="L92" s="3" t="inlineStr">
         <is>
-          <t>575ab</t>
+          <t>287ab</t>
         </is>
       </c>
     </row>
@@ -7006,7 +7006,7 @@
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>43.4ab</t>
+          <t>21.7ab</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="L93" s="3" t="inlineStr">
         <is>
-          <t>765ab</t>
+          <t>382ab</t>
         </is>
       </c>
     </row>
@@ -7066,7 +7066,7 @@
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>57.9ab</t>
+          <t>28.9ab</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="L94" s="3" t="inlineStr">
         <is>
-          <t>1.02ac</t>
+          <t>510ab</t>
         </is>
       </c>
     </row>
@@ -7126,7 +7126,7 @@
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>77.1ab</t>
+          <t>38.5ab</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="L95" s="3" t="inlineStr">
         <is>
-          <t>1.35ac</t>
+          <t>679ab</t>
         </is>
       </c>
     </row>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>102ab</t>
+          <t>51.3ab</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
@@ -7226,7 +7226,7 @@
       </c>
       <c r="L96" s="3" t="inlineStr">
         <is>
-          <t>1.8ac</t>
+          <t>904ab</t>
         </is>
       </c>
     </row>
@@ -7246,7 +7246,7 @@
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>136ab</t>
+          <t>68.4ab</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="L97" s="3" t="inlineStr">
         <is>
-          <t>2.41ac</t>
+          <t>1.2ac</t>
         </is>
       </c>
     </row>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>182ab</t>
+          <t>91.1ab</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="L98" s="3" t="inlineStr">
         <is>
-          <t>3.21ac</t>
+          <t>1.6ac</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>242ab</t>
+          <t>121ab</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="L99" s="3" t="inlineStr">
         <is>
-          <t>4.27ac</t>
+          <t>2.13ac</t>
         </is>
       </c>
     </row>
@@ -7426,7 +7426,7 @@
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>323ab</t>
+          <t>161ab</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="L100" s="3" t="inlineStr">
         <is>
-          <t>5.69ac</t>
+          <t>2.84ac</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>430ab</t>
+          <t>215ab</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="L101" s="3" t="inlineStr">
         <is>
-          <t>7.58ac</t>
+          <t>3.79ac</t>
         </is>
       </c>
     </row>
@@ -7546,7 +7546,7 @@
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>565ab</t>
+          <t>282ab</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
@@ -7586,7 +7586,7 @@
       </c>
       <c r="L102" s="3" t="inlineStr">
         <is>
-          <t>10.7ac</t>
+          <t>5.37ac</t>
         </is>
       </c>
     </row>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>701ab</t>
+          <t>350ab</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="L103" s="3" t="inlineStr">
         <is>
-          <t>13.3ac</t>
+          <t>6.66ac</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>870ab</t>
+          <t>435ab</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="L104" s="3" t="inlineStr">
         <is>
-          <t>16.5ac</t>
+          <t>8.26ac</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>1.07ac</t>
+          <t>539ab</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="L105" s="3" t="inlineStr">
         <is>
-          <t>20.5ac</t>
+          <t>10.2ac</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>1.33ac</t>
+          <t>669ab</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="L106" s="3" t="inlineStr">
         <is>
-          <t>25.4ac</t>
+          <t>12.7ac</t>
         </is>
       </c>
     </row>
@@ -7846,7 +7846,7 @@
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>1.65ac</t>
+          <t>829ab</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="L107" s="3" t="inlineStr">
         <is>
-          <t>31.5ac</t>
+          <t>15.7ac</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>2.05ac</t>
+          <t>1.02ac</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
@@ -7946,7 +7946,7 @@
       </c>
       <c r="L108" s="3" t="inlineStr">
         <is>
-          <t>39.1ac</t>
+          <t>19.5ac</t>
         </is>
       </c>
     </row>
@@ -7966,7 +7966,7 @@
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>2.55ac</t>
+          <t>1.27ac</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="L109" s="3" t="inlineStr">
         <is>
-          <t>48.5ac</t>
+          <t>24.2ac</t>
         </is>
       </c>
     </row>
@@ -8026,7 +8026,7 @@
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>3.16ac</t>
+          <t>1.58ac</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="L110" s="3" t="inlineStr">
         <is>
-          <t>60.1ac</t>
+          <t>30ac</t>
         </is>
       </c>
     </row>
@@ -8086,7 +8086,7 @@
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>3.92ac</t>
+          <t>1.96ac</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="L111" s="3" t="inlineStr">
         <is>
-          <t>74.6ac</t>
+          <t>37.3ac</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>4.87ac</t>
+          <t>2.43ac</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="L112" s="3" t="inlineStr">
         <is>
-          <t>92.5ac</t>
+          <t>46.2ac</t>
         </is>
       </c>
     </row>
@@ -8206,7 +8206,7 @@
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>6.04ac</t>
+          <t>3.02ac</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="L113" s="3" t="inlineStr">
         <is>
-          <t>114ac</t>
+          <t>57.4ac</t>
         </is>
       </c>
     </row>
@@ -8266,7 +8266,7 @@
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>7.49ac</t>
+          <t>3.74ac</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="L114" s="3" t="inlineStr">
         <is>
-          <t>142ac</t>
+          <t>71.2ac</t>
         </is>
       </c>
     </row>
@@ -8326,7 +8326,7 @@
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>9.29ac</t>
+          <t>4.64ac</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="L115" s="3" t="inlineStr">
         <is>
-          <t>176ac</t>
+          <t>88.3ac</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>11.5ac</t>
+          <t>5.76ac</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="L116" s="3" t="inlineStr">
         <is>
-          <t>219ac</t>
+          <t>109ac</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>14.2ac</t>
+          <t>7.14ac</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="L117" s="3" t="inlineStr">
         <is>
-          <t>271ac</t>
+          <t>135ac</t>
         </is>
       </c>
     </row>
@@ -8506,7 +8506,7 @@
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>17.7ac</t>
+          <t>8.86ac</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="L118" s="3" t="inlineStr">
         <is>
-          <t>336ac</t>
+          <t>168ac</t>
         </is>
       </c>
     </row>
@@ -8566,7 +8566,7 @@
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>21.9ac</t>
+          <t>10.9ac</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="L119" s="3" t="inlineStr">
         <is>
-          <t>417ac</t>
+          <t>208ac</t>
         </is>
       </c>
     </row>
@@ -8626,7 +8626,7 @@
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>27.2ac</t>
+          <t>13.6ac</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="L120" s="3" t="inlineStr">
         <is>
-          <t>518ac</t>
+          <t>259ac</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>33.8ac</t>
+          <t>16.9ac</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="L121" s="3" t="inlineStr">
         <is>
-          <t>642ac</t>
+          <t>321ac</t>
         </is>
       </c>
     </row>
@@ -8746,7 +8746,7 @@
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>41.9ac</t>
+          <t>20.9ac</t>
         </is>
       </c>
       <c r="E122" s="3" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="L122" s="3" t="inlineStr">
         <is>
-          <t>797ac</t>
+          <t>398ac</t>
         </is>
       </c>
     </row>
@@ -8806,7 +8806,7 @@
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>52ac</t>
+          <t>26ac</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
@@ -8846,7 +8846,7 @@
       </c>
       <c r="L123" s="3" t="inlineStr">
         <is>
-          <t>988ac</t>
+          <t>494ac</t>
         </is>
       </c>
     </row>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>64.5ac</t>
+          <t>32.2ac</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="L124" s="3" t="inlineStr">
         <is>
-          <t>1.22ad</t>
+          <t>613ac</t>
         </is>
       </c>
     </row>
@@ -8926,7 +8926,7 @@
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>80ac</t>
+          <t>40ac</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="L125" s="3" t="inlineStr">
         <is>
-          <t>1.52ad</t>
+          <t>760ac</t>
         </is>
       </c>
     </row>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>99.2ac</t>
+          <t>49.6ac</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
@@ -9026,7 +9026,7 @@
       </c>
       <c r="L126" s="3" t="inlineStr">
         <is>
-          <t>1.88ad</t>
+          <t>943ac</t>
         </is>
       </c>
     </row>
@@ -9046,7 +9046,7 @@
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>123ac</t>
+          <t>61.5ac</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="L127" s="3" t="inlineStr">
         <is>
-          <t>2.33ad</t>
+          <t>1.16ad</t>
         </is>
       </c>
     </row>
@@ -9106,7 +9106,7 @@
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>152ac</t>
+          <t>76.3ac</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
@@ -9146,7 +9146,7 @@
       </c>
       <c r="L128" s="3" t="inlineStr">
         <is>
-          <t>2.9ad</t>
+          <t>1.45ad</t>
         </is>
       </c>
     </row>
@@ -9166,7 +9166,7 @@
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>189ac</t>
+          <t>94.6ac</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="L129" s="3" t="inlineStr">
         <is>
-          <t>3.59ad</t>
+          <t>1.79ad</t>
         </is>
       </c>
     </row>
@@ -9226,7 +9226,7 @@
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>234ac</t>
+          <t>117ac</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
@@ -9266,7 +9266,7 @@
       </c>
       <c r="L130" s="3" t="inlineStr">
         <is>
-          <t>4.46ad</t>
+          <t>2.23ad</t>
         </is>
       </c>
     </row>
@@ -9286,7 +9286,7 @@
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>291ac</t>
+          <t>145ac</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="L131" s="3" t="inlineStr">
         <is>
-          <t>5.53ad</t>
+          <t>2.76ad</t>
         </is>
       </c>
     </row>
@@ -9346,7 +9346,7 @@
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>361ac</t>
+          <t>180ac</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="L132" s="3" t="inlineStr">
         <is>
-          <t>6.86ad</t>
+          <t>3.43ad</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>447ac</t>
+          <t>223ac</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
@@ -9446,7 +9446,7 @@
       </c>
       <c r="L133" s="3" t="inlineStr">
         <is>
-          <t>8.51ad</t>
+          <t>4.25ad</t>
         </is>
       </c>
     </row>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>555ac</t>
+          <t>277ac</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
@@ -9506,7 +9506,7 @@
       </c>
       <c r="L134" s="3" t="inlineStr">
         <is>
-          <t>10.5ad</t>
+          <t>5.27ad</t>
         </is>
       </c>
     </row>
@@ -9526,7 +9526,7 @@
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>688ac</t>
+          <t>344ac</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="L135" s="3" t="inlineStr">
         <is>
-          <t>13ad</t>
+          <t>6.54ad</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>854ac</t>
+          <t>427ac</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
@@ -9626,7 +9626,7 @@
       </c>
       <c r="L136" s="3" t="inlineStr">
         <is>
-          <t>16.2ad</t>
+          <t>8.11ad</t>
         </is>
       </c>
     </row>
@@ -9646,7 +9646,7 @@
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>1.05ad</t>
+          <t>529ac</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
@@ -9686,7 +9686,7 @@
       </c>
       <c r="L137" s="3" t="inlineStr">
         <is>
-          <t>20.1ad</t>
+          <t>10ad</t>
         </is>
       </c>
     </row>
@@ -9706,7 +9706,7 @@
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>1.31ad</t>
+          <t>657ac</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="L138" s="3" t="inlineStr">
         <is>
-          <t>24.9ad</t>
+          <t>12.4ad</t>
         </is>
       </c>
     </row>
@@ -9766,7 +9766,7 @@
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>1.62ad</t>
+          <t>814ac</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
@@ -9806,7 +9806,7 @@
       </c>
       <c r="L139" s="3" t="inlineStr">
         <is>
-          <t>30.9ad</t>
+          <t>15.4ad</t>
         </is>
       </c>
     </row>
@@ -9826,7 +9826,7 @@
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>2.02ad</t>
+          <t>1.01ad</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="L140" s="3" t="inlineStr">
         <is>
-          <t>38.4ad</t>
+          <t>19.2ad</t>
         </is>
       </c>
     </row>
@@ -9886,7 +9886,7 @@
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>2.5ad</t>
+          <t>1.25ad</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
@@ -9926,7 +9926,7 @@
       </c>
       <c r="L141" s="3" t="inlineStr">
         <is>
-          <t>47.6ad</t>
+          <t>23.8ad</t>
         </is>
       </c>
     </row>
@@ -9946,7 +9946,7 @@
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>3.1ad</t>
+          <t>1.55ad</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
@@ -9986,7 +9986,7 @@
       </c>
       <c r="L142" s="3" t="inlineStr">
         <is>
-          <t>59ad</t>
+          <t>29.5ad</t>
         </is>
       </c>
     </row>
@@ -10006,7 +10006,7 @@
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>3.85ad</t>
+          <t>1.92ad</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
@@ -10046,7 +10046,7 @@
       </c>
       <c r="L143" s="3" t="inlineStr">
         <is>
-          <t>73.2ad</t>
+          <t>36.6ad</t>
         </is>
       </c>
     </row>
@@ -10066,7 +10066,7 @@
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>4.78ad</t>
+          <t>2.39ad</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
@@ -10106,7 +10106,7 @@
       </c>
       <c r="L144" s="3" t="inlineStr">
         <is>
-          <t>90.9ad</t>
+          <t>45.4ad</t>
         </is>
       </c>
     </row>
@@ -10126,7 +10126,7 @@
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>5.93ad</t>
+          <t>2.96ad</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="L145" s="3" t="inlineStr">
         <is>
-          <t>112ad</t>
+          <t>56.3ad</t>
         </is>
       </c>
     </row>
@@ -10186,7 +10186,7 @@
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>7.35ad</t>
+          <t>3.67ad</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="L146" s="3" t="inlineStr">
         <is>
-          <t>139ad</t>
+          <t>69.9ad</t>
         </is>
       </c>
     </row>
@@ -10246,7 +10246,7 @@
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>9.12ad</t>
+          <t>4.56ad</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="L147" s="3" t="inlineStr">
         <is>
-          <t>173ad</t>
+          <t>86.7ad</t>
         </is>
       </c>
     </row>
@@ -10306,7 +10306,7 @@
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>11.3ad</t>
+          <t>5.65ad</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
@@ -10346,7 +10346,7 @@
       </c>
       <c r="L148" s="3" t="inlineStr">
         <is>
-          <t>215ad</t>
+          <t>107ad</t>
         </is>
       </c>
     </row>
@@ -10366,7 +10366,7 @@
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>14ad</t>
+          <t>7.01ad</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="L149" s="3" t="inlineStr">
         <is>
-          <t>266ad</t>
+          <t>133ad</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>17.4ad</t>
+          <t>8.7ad</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="L150" s="3" t="inlineStr">
         <is>
-          <t>330ad</t>
+          <t>165ad</t>
         </is>
       </c>
     </row>
@@ -10486,7 +10486,7 @@
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>21.5ad</t>
+          <t>10.7ad</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
@@ -10526,7 +10526,7 @@
       </c>
       <c r="L151" s="3" t="inlineStr">
         <is>
-          <t>410ad</t>
+          <t>205ad</t>
         </is>
       </c>
     </row>
